--- a/main/ig/StructureDefinition-FRLMFamilyMemberHistory.xlsx
+++ b/main/ig/StructureDefinition-FRLMFamilyMemberHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T14:19:44+00:00</t>
+    <t>2026-09-14T09:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-FRLMFamilyMemberHistory.xlsx
+++ b/main/ig/StructureDefinition-FRLMFamilyMemberHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T09:04:12+00:00</t>
+    <t>2026-09-23T09:36:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-FRLMFamilyMemberHistory.xlsx
+++ b/main/ig/StructureDefinition-FRLMFamilyMemberHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:36:17+00:00</t>
+    <t>2026-09-28T10:07:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-FRLMFamilyMemberHistory.xlsx
+++ b/main/ig/StructureDefinition-FRLMFamilyMemberHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:07:47+00:00</t>
+    <t>2026-09-30T20:10:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -283,7 +283,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l’entrée</t>
+    <t>Identifiant</t>
   </si>
   <si>
     <t>FRLMEntry.header.identifier</t>
@@ -425,7 +425,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>Statut de l'entrée provenant du jdv FHIR https://hl7.org/fhir/R4/valueset-history-status</t>
+    <t>Statut provenant du jdv FHIR https://hl7.org/fhir/R4/valueset-history-status</t>
   </si>
   <si>
     <t>https://hl7.org/fhir/R4/valueset-history-status.html</t>
@@ -566,7 +566,7 @@
     <t>Statut provenant du jdv-health-status-code-cisis (1.2.250.1.213.1.1.4.2.283.1)</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-health-status-code-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-health-status-code-cisis|20260916095455</t>
   </si>
   <si>
     <t>FRLMFamilyMemberHistory.condition.contributedToDeath</t>
@@ -931,7 +931,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="68.81640625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="62.59375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="68.78125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-FRLMFamilyMemberHistory.xlsx
+++ b/main/ig/StructureDefinition-FRLMFamilyMemberHistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:10:21+00:00</t>
+    <t>2026-10-08T12:56:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
